--- a/auditoria_paneles_qaway_hub.xlsx
+++ b/auditoria_paneles_qaway_hub.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\LEO\EMPRESAS\QAWAY LAB\1-QawayLab-Digital\1-qawaylab-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E906A349-49B8-4870-970D-2E5DB3CF5C85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{392E5652-564C-4B97-AEB0-25985B1ACEA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="2040" windowWidth="18612" windowHeight="10200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Auditoria_Paneles" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="124">
   <si>
     <t>ID</t>
   </si>
@@ -1028,7 +1028,13 @@
         <v>44</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>17</v>
+        <v>119</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="62.4" x14ac:dyDescent="0.3">
